--- a/services_forms/009_crowd_funding_forms--services_forms.xlsx
+++ b/services_forms/009_crowd_funding_forms--services_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -510,15 +510,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>crowd_funding_form</t>
+          <t>main_project_form</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CrowdFundingForm</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Project Information</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please provide your project details below.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -533,18 +537,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>form_1_name</t>
+          <t>main_project_form_contact_info</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FormName</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Main Project Contact Information</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Your contact information is private.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -556,18 +564,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>form_1_email</t>
+          <t>main_project_form_contact_name</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Main Project Contact Name</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Your contact name should match your name on this form.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -579,87 +591,103 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_1_phone</t>
+          <t>main_project_form_contact_email</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Main Project Contact Email</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>We will use this for communication.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_1_date</t>
+          <t>main_project_form_contact_phone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Main Project Contact Phone Number</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>We will use this for communication.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_1_time</t>
+          <t>main_project_form_deadline</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Main Project Deadline</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>When is the deadline for the project?</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_1_notes</t>
+          <t>main_project_form_timeframe</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Main Project Timeframe</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>What is the timeframe for the project?</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -671,12 +699,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>form_2_name</t>
+          <t>backer_info_form</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Backer's Information</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -694,15 +722,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>form_2_email</t>
+          <t>backer_info_form_contact_email</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Backer's Contact Email</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>We will use this for communication.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -717,15 +749,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>form_2_phone</t>
+          <t>backer_info_form_contact_phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Backer's Contact Phone Number</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>We will use this for communication.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -735,20 +771,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>form_2_date</t>
+          <t>backer_info_form_notes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Backer's Notes</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Any additional notes.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -758,44 +798,79 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>form_2_time</t>
+          <t>backer_info_form_confirmation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Backer's Confirmation</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please confirm your contact information.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>backer_info_form_agreement</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Backer's Agreement</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please agree to our terms and conditions.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>form_2_notes</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>backer_info_form_notes2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Backer's Notes 2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Any additional notes.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
         </is>
